--- a/AAAGameData/DataTables/Tech/TechNodeTable.xlsx
+++ b/AAAGameData/DataTables/Tech/TechNodeTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="101">
   <si>
     <t>#</t>
   </si>
@@ -56,9 +56,6 @@
     <t>CostMaterial</t>
   </si>
   <si>
-    <t>Effects</t>
-  </si>
-  <si>
     <t>AllConditions</t>
   </si>
   <si>
@@ -68,10 +65,10 @@
     <t>SpriteName</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
+    <t>NameKey</t>
+  </si>
+  <si>
+    <t>DescriptionKey</t>
   </si>
   <si>
     <t>int</t>
@@ -89,10 +86,7 @@
     <t>StringIntPair[]</t>
   </si>
   <si>
-    <t>TechEffect[]</t>
-  </si>
-  <si>
-    <t>TechCondition[]</t>
+    <t>UnlockCondition[]</t>
   </si>
   <si>
     <r>
@@ -135,9 +129,6 @@
     <t>材料消耗</t>
   </si>
   <si>
-    <t>效果串</t>
-  </si>
-  <si>
     <t>AND 条件串</t>
   </si>
   <si>
@@ -153,7 +144,7 @@
     <t>节点描述(多语言)</t>
   </si>
   <si>
-    <t>TechNode_Aaa1</t>
+    <t>TechNode_InfoUnderstand_1</t>
   </si>
   <si>
     <t>TechCategory.Explore</t>
@@ -165,13 +156,13 @@
     <t>UI/IconMisc/Icon_Star_On.png</t>
   </si>
   <si>
-    <t>TechNode.Name.Aaa</t>
-  </si>
-  <si>
-    <t>TechNode.Description.Aaa</t>
-  </si>
-  <si>
-    <t>TechNode_Aaa2</t>
+    <t>TechNode.Name.InfoUnderstand_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.InfoUnderstand_1</t>
+  </si>
+  <si>
+    <t>TechNode_Map_1</t>
   </si>
   <si>
     <t>[Material_Aaa, 2],[Material_Bbb, 4]</t>
@@ -180,13 +171,13 @@
     <t>UI/IconMisc/Icon_Star_Off.png</t>
   </si>
   <si>
-    <t>TechNode.Name.Bbb</t>
-  </si>
-  <si>
-    <t>TechNode.Description.Bbb</t>
-  </si>
-  <si>
-    <t>TechNode_Aaa3</t>
+    <t>TechNode.Name.Map_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.Map_1</t>
+  </si>
+  <si>
+    <t>TechNode_Map_2</t>
   </si>
   <si>
     <t>[Material_Aaa, 2],[Material_Bbb, 5]</t>
@@ -195,43 +186,169 @@
     <t>UI/IconMisc/Icon_Setting.png</t>
   </si>
   <si>
-    <t>TechNode.Name.Ccc</t>
-  </si>
-  <si>
-    <t>TechNode.Description.Ccc</t>
-  </si>
-  <si>
-    <t>TechNode_Bbb</t>
+    <t>TechNode.Name.Map_2</t>
+  </si>
+  <si>
+    <t>TechNode.Description.Map_2</t>
+  </si>
+  <si>
+    <t>TechNode_Map_3</t>
+  </si>
+  <si>
+    <t>[Material_Aaa, 2],[Material_Bbb, 6],[Material_Ddd, 3]</t>
+  </si>
+  <si>
+    <t>UI/IconMisc/Icon_Close02.png</t>
+  </si>
+  <si>
+    <t>TechNode.Name.Map_3</t>
+  </si>
+  <si>
+    <t>TechNode.Description.Map_3</t>
+  </si>
+  <si>
+    <t>TechNode_DungeonTicket_1</t>
+  </si>
+  <si>
+    <t>UI/IconMisc/Icon_Check03_s.png</t>
+  </si>
+  <si>
+    <t>TechNode.Name.DungeonTicket_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.DungeonTicket_1</t>
+  </si>
+  <si>
+    <t>TechNode_CharUpgradeDevice_1</t>
   </si>
   <si>
     <t>TechCategory.Fight</t>
   </si>
   <si>
-    <t>[Material_Aaa, 2],[Material_Bbb, 6],[Material_Ddd, 3]</t>
-  </si>
-  <si>
-    <t>UI/IconMisc/Icon_Close02.png</t>
-  </si>
-  <si>
-    <t>TechNode.Name.Ddd</t>
-  </si>
-  <si>
-    <t>TechNode.Description.Ddd</t>
-  </si>
-  <si>
-    <t>TechNode_Ccc</t>
+    <t>[Material_Ccc, 2]</t>
+  </si>
+  <si>
+    <t>TechNode.Name.CharUpgradeDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.CharUpgradeDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode_SkillUpgradeDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.SkillUpgradeDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.SkillUpgradeDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode_ApplyAttackingDelay_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.ApplyAttackingDelay_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.ApplyAttackingDelay_1</t>
+  </si>
+  <si>
+    <t>TechNode_EquipmentCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechCategory.Craft</t>
+  </si>
+  <si>
+    <t>TechNode.Name.EquipmentCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.EquipmentCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode_ConsumableCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.ConsumableCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.ConsumableCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode_MiscCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.MiscCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.MiscCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode_BaseHeal_1</t>
+  </si>
+  <si>
+    <t>TechCategory.Efficiency</t>
+  </si>
+  <si>
+    <t>TechNode.Name.BaseHeal_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.BaseHeal_1</t>
+  </si>
+  <si>
+    <t>TechNode_CheckpointHeal_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.CheckpointHeal_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.CheckpointHeal_1</t>
+  </si>
+  <si>
+    <t>TechNode_Manual_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.Manual_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.Manual_1</t>
+  </si>
+  <si>
+    <t>TechNode_ViewEnemyInfo_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.ViewEnemyInfo_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.ViewEnemyInfo_1</t>
+  </si>
+  <si>
+    <t>TechNode_ViewEnemyInfo_2</t>
+  </si>
+  <si>
+    <t>TechNode.Name.ViewEnemyInfo_2</t>
+  </si>
+  <si>
+    <t>TechNode.Description.ViewEnemyInfo_2</t>
+  </si>
+  <si>
+    <t>TechNode_ToolCraftingDevice_1</t>
   </si>
   <si>
     <t>TechCategory.Profit</t>
   </si>
   <si>
-    <t>UI/IconMisc/Icon_Check03_s.png</t>
-  </si>
-  <si>
-    <t>TechNode.Name.Eee</t>
-  </si>
-  <si>
-    <t>TechNode.Description.Eee</t>
+    <t>TechNode.Name.ToolCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.ToolCraftingDevice_1</t>
+  </si>
+  <si>
+    <t>TechNode_CritCollecting_1</t>
+  </si>
+  <si>
+    <t>TechNode.Name.CritCollecting_1</t>
+  </si>
+  <si>
+    <t>TechNode.Description.CritCollecting_1</t>
   </si>
 </sst>
 </file>
@@ -860,12 +977,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1187,7 +1301,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1195,28 +1309,28 @@
     <col min="3" max="3" width="5.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.8333333333333" style="1" customWidth="1"/>
     <col min="5" max="8" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="10" width="22.4166666666667" style="1" customWidth="1"/>
-    <col min="11" max="12" width="16.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="23.25" style="1" customWidth="1"/>
-    <col min="14" max="14" width="29.5833333333333" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="1"/>
+    <col min="9" max="9" width="22.4166666666667" style="1" customWidth="1"/>
+    <col min="10" max="11" width="16.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29.5833333333333" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,233 +1367,562 @@
       <c r="M2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" ht="28.75" spans="2:14">
+    </row>
+    <row r="5" ht="28.75" spans="2:13">
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
+      <c r="M5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="L5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" ht="28.75" spans="2:14">
+    </row>
+    <row r="6" ht="28.75" spans="2:13">
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="M6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="L6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" ht="28.75" spans="2:14">
+    </row>
+    <row r="7" ht="28.75" spans="2:13">
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="M7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="L7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" ht="28.75" spans="2:14">
+    </row>
+    <row r="8" ht="28.75" spans="2:13">
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="M8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="L8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" ht="28.75" spans="2:14">
+    </row>
+    <row r="9" ht="28.75" spans="2:13">
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="28.75" spans="2:13">
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
         <v>58</v>
       </c>
-      <c r="H9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="H10" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="K10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="11" ht="28.75" spans="2:13">
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" ht="28.75" spans="2:13">
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" ht="28.75" spans="2:13">
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" ht="28.75" spans="2:13">
+      <c r="B14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" ht="28.75" spans="2:13">
+      <c r="B15" s="1">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" ht="28.75" spans="2:13">
+      <c r="B16" s="1">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" ht="28.75" spans="2:13">
+      <c r="B17" s="1">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s">
+        <v>59</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" ht="28.75" spans="2:13">
+      <c r="B18" s="1">
+        <v>14</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" ht="28.75" spans="2:13">
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s">
+        <v>59</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" ht="28.75" spans="2:13">
+      <c r="B20" s="1">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" ht="28.75" spans="2:13">
+      <c r="B21" s="1">
+        <v>17</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" ht="28.75" spans="2:13">
+      <c r="B22" s="1">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
